--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -8899,7 +8899,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산관리부서 기록철 | 보존기간: 3년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -9795,7 +9795,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 자재구매부서 기록철 | 보존기간: 3년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -1136,7 +1136,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="92" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | SH-FM-101~SH-FM-121 | Rev.03 | 양식 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | SH-FM-101~SH-FM-121 | Rev.03 | 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -1148,7 +1148,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="92" t="inlineStr">
         <is>
-          <t>사용 순서: 해당 시트 선택 → 건별 복사·저장 → 실제 결과 입력 → 확인·결재 → 부서 기록철 보관</t>
+          <t>사용 순서: 해당 시트 선택 → 건별 복사·저장 → 실제 결과 입력 → 확인·결재 → 품질팀 서버 보관</t>
         </is>
       </c>
       <c r="B3" s="90" t="n"/>
@@ -2016,7 +2016,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-109 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-109 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2415,7 +2415,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -2508,7 +2508,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-110 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-110 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -2956,7 +2956,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-111 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-111 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -3320,7 +3320,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -3409,7 +3409,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-112 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-112 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -3793,7 +3793,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산관리부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -3882,7 +3882,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-113 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-113 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -4246,7 +4246,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -4335,7 +4335,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-114 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-114 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -4719,7 +4719,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 자재구매부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -4808,7 +4808,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-115 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-115 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -5192,7 +5192,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -5281,7 +5281,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-116 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-116 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -5665,7 +5665,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -5754,7 +5754,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-117 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-117 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -6138,7 +6138,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -6235,7 +6235,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-118 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-118 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -6599,7 +6599,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 자재구매부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -6683,7 +6683,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-101 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-101 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7047,7 +7047,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 설비관리 담당부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -7136,7 +7136,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-119 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-119 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7520,7 +7520,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -7614,7 +7614,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-120 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-120 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7998,7 +7998,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -8087,7 +8087,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-121 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-121 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -8451,7 +8451,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 교육 주관부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -8983,7 +8983,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-103 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-103 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -9347,7 +9347,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 설비관리 담당부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -9879,7 +9879,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-105 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-105 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -10263,7 +10263,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산관리부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -10357,7 +10357,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-106 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-106 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -10741,7 +10741,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -10835,7 +10835,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-107 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-107 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -11199,7 +11199,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -11288,7 +11288,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-108 | Rev.03 | 문서상태: 승인완료 | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-108 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -11652,7 +11652,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 생산부서 기록철 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -1184,7 +1184,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="92" t="inlineStr">
         <is>
-          <t>규격·점검기준·허용범위는 승인된 도면·Control Plan·작업표준에서 입력합니다. 보존기간은 전 양식 5년으로 확정합니다.</t>
+          <t>규격·점검기준·허용범위는 승인된 도면·Control Plan·작업표준에서 입력합니다. 보존기간은 전 양식 3년으로 정합합니다(개정 초안).</t>
         </is>
       </c>
       <c r="B6" s="90" t="n"/>
@@ -2415,7 +2415,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -3320,7 +3320,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -3793,7 +3793,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -4246,7 +4246,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -4719,7 +4719,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -5192,7 +5192,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -5665,7 +5665,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -6138,7 +6138,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -6599,7 +6599,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -7047,7 +7047,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -7520,7 +7520,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -7998,7 +7998,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -8451,7 +8451,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -9347,7 +9347,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -10263,7 +10263,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -10741,7 +10741,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -11199,7 +11199,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>
@@ -11652,7 +11652,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>보관위치(안): 품질팀 서버 | 보존기간: 5년</t>
+          <t>보관위치(안): 품질팀 서버 | 보존기간: 3년</t>
         </is>
       </c>
       <c r="B31" s="90" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="00_안내및목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SH-FM-101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SH-FM-102" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SH-FM-103" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SH-FM-104" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SH-FM-105" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SH-FM-106" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SH-FM-107" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SH-FM-108" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SH-FM-109" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SH-FM-110" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="SH-FM-111" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="SH-FM-112" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SH-FM-113" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SH-FM-114" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="SH-FM-115" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SH-FM-116" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="SH-FM-117" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="SH-FM-118" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="SH-FM-119" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="SH-FM-120" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="SH-FM-121" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_안내및목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-101" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-102" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-103" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-104" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-105" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-106" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-107" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-108" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-109" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-110" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-111" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-112" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-113" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-114" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-115" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-116" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-117" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-118" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-119" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-120" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-121" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="B9" s="45" t="inlineStr">
         <is>
-          <t>입고 LOT / 공급사 LOT</t>
+          <t>입고 LOT / 공급자 LOT</t>
         </is>
       </c>
       <c r="C9" s="45" t="inlineStr">
@@ -9683,7 +9683,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="95" t="inlineStr">
         <is>
-          <t>작성 안내: 품번·단위별로 사용하며 잔량은 실제 재고와 대조합니다. 입고 시 입고 LOT(L+입고일 YYMMDD-일별순번)와 공급사 LOT를 함께 기록합니다(SH-QP-018). 보존기간 기산점은 입고일입니다.</t>
+          <t>작성 안내: 품번·단위별로 사용하며 잔량은 실제 재고와 대조합니다. 입고 시 입고 LOT(L+입고일 YYMMDD-일별순번)와 공급자 LOT를 함께 기록합니다(SH-QP-018). 보존기간 기산점은 입고일입니다.</t>
         </is>
       </c>
       <c r="B23" s="96" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -1136,7 +1136,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="92" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | SH-FM-101~SH-FM-121 | Rev.03 | 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | SH-FM-101~SH-FM-121 | Rev.03 | 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2016,7 +2016,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-109 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-109 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2508,7 +2508,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-110 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-110 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2956,7 +2956,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-111 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-111 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -3409,7 +3409,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-112 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-112 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -3882,7 +3882,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-113 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-113 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -4335,7 +4335,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-114 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-114 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -4808,7 +4808,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-115 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-115 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -5281,7 +5281,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-116 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-116 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -5754,7 +5754,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-117 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-117 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -6235,7 +6235,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-118 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-118 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -6683,7 +6683,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-101 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-101 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7136,7 +7136,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-119 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-119 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7614,7 +7614,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-120 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-120 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -8087,7 +8087,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-121 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-121 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -8535,7 +8535,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-102 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-102 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -8983,7 +8983,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-103 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-103 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -9431,7 +9431,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-104 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-104 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -9879,7 +9879,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-105 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-105 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -10357,7 +10357,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-106 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-106 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -10835,7 +10835,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-107 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-107 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -11288,7 +11288,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-108 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-108 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -26,7 +26,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-120" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH-FM-121" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'00_안내및목록'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'SH-FM-101'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SH-FM-102'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'SH-FM-103'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'SH-FM-104'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'SH-FM-105'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'SH-FM-106'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'SH-FM-107'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'SH-FM-108'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'SH-FM-109'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'SH-FM-110'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'SH-FM-111'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'SH-FM-112'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'SH-FM-113'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'SH-FM-114'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'SH-FM-115'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'SH-FM-116'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'SH-FM-117'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'SH-FM-118'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'SH-FM-119'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'SH-FM-120'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'SH-FM-121'!$A$1:$F$32</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -1108,7 +1131,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1980,7 +2003,9 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1988,7 +2013,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2472,7 +2497,9 @@
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2480,7 +2507,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2920,7 +2947,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2928,7 +2957,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3373,7 +3402,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3381,7 +3412,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3846,7 +3877,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3854,7 +3887,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4299,7 +4332,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4307,7 +4342,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4772,7 +4807,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4780,7 +4817,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5245,7 +5282,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5253,7 +5292,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5718,7 +5757,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5726,7 +5767,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6199,7 +6240,9 @@
       <formula1>"적합,부적합,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6207,7 +6250,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6647,7 +6690,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6655,7 +6700,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7100,7 +7145,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7108,7 +7155,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7578,7 +7625,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7586,7 +7635,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8051,7 +8100,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8059,7 +8110,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8499,7 +8550,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8507,7 +8560,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8947,7 +9000,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8955,7 +9010,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9395,7 +9450,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -9403,7 +9460,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9843,7 +9900,9 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -9851,7 +9910,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10321,7 +10380,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10329,7 +10390,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10799,7 +10860,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10807,7 +10870,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -11252,7 +11315,9 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -11260,7 +11325,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -11705,6 +11770,8 @@
       <formula1>"적합,부적합,해당없음,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-101-121_현장작성양식_Rev03_LOT정합_DRAFT.xlsx
@@ -1159,7 +1159,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="92" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | SH-FM-101~SH-FM-121 | Rev.03 | 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | SH-FM-101~SH-FM-121 | Rev.03 | 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2041,7 +2041,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-109 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-109 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2535,7 +2535,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-110 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-110 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -2985,7 +2985,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-111 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-111 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -3440,7 +3440,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-112 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-112 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -3915,7 +3915,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-113 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-113 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -4370,7 +4370,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-114 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-114 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -4845,7 +4845,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-115 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-115 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -5320,7 +5320,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-116 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-116 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -5795,7 +5795,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-117 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-117 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -6278,7 +6278,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-118 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-118 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -6728,7 +6728,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-101 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-101 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7183,7 +7183,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-119 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-119 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -7663,7 +7663,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-120 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-120 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -8138,7 +8138,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-121 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-121 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -8588,7 +8588,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-102 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-102 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -9038,7 +9038,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-103 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-103 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -9488,7 +9488,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-104 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-104 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -9938,7 +9938,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-105 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-105 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -10418,7 +10418,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-106 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-106 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -10898,7 +10898,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-107 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-107 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
@@ -11353,7 +11353,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
         <is>
-          <t>(주)신화에이치앤티 | 문서번호 SH-FM-108 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 담당자 확정 후 지정</t>
+          <t>(주)신화에이치앤티 | 문서번호 SH-FM-108 | Rev.03 | 문서상태: 개정초안(미승인) | 제정일: 2026-09-01 | 개정일: 2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="90" t="n"/>
